--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/07-chefs-table-eventos.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/07-chefs-table-eventos.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chef's Table" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pop-ups" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cenas Especiales" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chef's Table" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pop-ups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cenas Especiales" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Chef''s Table'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Pop-ups'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cenas Especiales'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +85,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -163,60 +172,71 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -576,15 +596,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -592,6 +613,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -627,9 +649,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -672,8 +692,25 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -682,18 +719,18 @@
   <sheetPr>
     <tabColor rgb="0000BCD4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -710,6 +747,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -868,6 +906,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1025,6 +1064,26 @@
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="11" t="n"/>
       <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C21">
+        <f>COUNTIF(E6:E20,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E21">
+        <f>COUNTIF(B6:B20,"?*")</f>
+        <v>13.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
@@ -1049,12 +1108,26 @@
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G20">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1063,18 +1136,18 @@
   <sheetPr>
     <tabColor rgb="0000BCD4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1091,6 +1164,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1249,6 +1323,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1387,6 +1462,26 @@
       <c r="E19" s="12" t="n"/>
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C20">
+        <f>COUNTIF(E6:E19,"✓")</f>
+        <v>1.0</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E20">
+        <f>COUNTIF(B6:B19,"?*")</f>
+        <v>12.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
@@ -1411,12 +1506,26 @@
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G19">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1425,18 +1534,18 @@
   <sheetPr>
     <tabColor rgb="0000BCD4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1453,6 +1562,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1611,6 +1721,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1750,6 +1861,7 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -1869,6 +1981,26 @@
       <c r="E26" s="12" t="n"/>
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C27">
+        <f>COUNTIF(E6:E26,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E27">
+        <f>COUNTIF(B6:B26,"?*")</f>
+        <v>17.0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
@@ -1894,11 +2026,25 @@
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/07-chefs-table-eventos.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/07-chefs-table-eventos.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -694,9 +694,45 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Antes de aceptar una reserva privada:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>▸ La primera sección de «Cenas Especiales» es lo que se pacta AL CONFIRMAR: alérgenos e intolerancias por escrito, número de comensales cerrado, precio por comensal, señal y condiciones de cancelación. Lo de palabra no se puede demostrar después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>▸ Los alérgenos llegan por escrito y se resuelven con cocina antes de cerrar el menú, no la misma noche: en un degustación de diez pases, una alternativa improvisada rompe la secuencia entera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>▸ La noche de la cena no se vuelve a «confirmar» nada: lo que se hace en el pase es COTEJAR los alérgenos ya confirmados por escrito con la comanda de cada comensal. Uno pacta y el otro comprueba; no son dos veces el mismo control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-restaurante-creativo · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -798,7 +834,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Confirmar número de comensales y alérgenos</t>
+          <t>Repasar con cocina el número final de comensales y los alérgenos ya confirmados por escrito al reservar (ver «Cenas Especiales» → «AL CONFIRMAR LA RESERVA»)</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1072,8 +1108,8 @@
         </is>
       </c>
       <c r="C21">
-        <f>COUNTIF(E6:E20,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B20,"?*",E6:E20,"✓")-COUNTIFS(B6:B20,"Tarea",E6:E20,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1081,8 +1117,8 @@
         </is>
       </c>
       <c r="E21">
-        <f>COUNTIF(B6:B20,"?*")</f>
-        <v>13.0</v>
+        <f>COUNTIF(B6:B20,"?*")-COUNTIF(B6:B20,"Tarea")-COUNTIF(E6:E20,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
     <row r="22">
@@ -1114,8 +1150,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1470,8 +1506,8 @@
         </is>
       </c>
       <c r="C20">
-        <f>COUNTIF(E6:E19,"✓")</f>
-        <v>1.0</v>
+        <f>COUNTIFS(B6:B19,"?*",E6:E19,"✓")-COUNTIFS(B6:B19,"Tarea",E6:E19,"✓")</f>
+        <v>0.0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1479,8 +1515,8 @@
         </is>
       </c>
       <c r="E20">
-        <f>COUNTIF(B6:B19,"?*")</f>
-        <v>12.0</v>
+        <f>COUNTIF(B6:B19,"?*")-COUNTIF(B6:B19,"Tarea")-COUNTIF(E6:E19,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
     <row r="21">
@@ -1512,8 +1548,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1536,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1725,7 +1761,7 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>🕯️ CENAS PRIVADAS</t>
+          <t>📝 AL CONFIRMAR LA RESERVA (cena privada, evento o chef's table)</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1808,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Menú personalizado según solicitud del cliente</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Cocina</t>
+          <t>Alérgenos e intolerancias de TODOS los comensales por escrito (correo o formulario), nunca de palabra, y con nombre de la mesa</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D15" s="11" t="n"/>
@@ -1791,12 +1827,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Alérgenos y preferencias confirmados</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>Cocina</t>
+          <t>Número de comensales cerrado y fecha límite para cambios, anotada en la ficha del evento</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D16" s="11" t="n"/>
@@ -1810,12 +1846,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Servicio exclusivo: personal asignado</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Servicio</t>
+          <t>Precio por comensal y qué incluye (menú, maridaje, extras, servicio, IVA) confirmado por escrito</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D17" s="11" t="n"/>
@@ -1829,12 +1865,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Decoración especial de la mesa/sala</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Sala</t>
+          <t>Señal o anticipo cobrado y condiciones de cancelación aceptadas por escrito</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -1848,12 +1884,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto aprobado y facturación preparada</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Menú definitivo cerrado con cocina, con las alternativas de cada alérgeno ya resueltas y probadas</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D19" s="11" t="n"/>
@@ -1861,11 +1897,29 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
     </row>
-    <row r="20"/>
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Peticiones especiales anotadas en la ficha: dieta, celebración, decoración, tarta, horario de salida</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="13" t="n"/>
+    </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>📅 CALENDARIO ANUAL DE EVENTOS</t>
+          <t>🕯️ CENAS PRIVADAS</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1966,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Planificar eventos por trimestre (mín. 1/mes)</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Eventos</t>
+          <t>Producir el menú ya cerrado con el cliente: pedido específico, mise en place y prueba de los pases exclusivos de esta mesa</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D23" s="11" t="n"/>
@@ -1931,12 +1985,12 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto anual de eventos especiales</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Cotejar en el pase los alérgenos confirmados por escrito con la comanda de cada comensal</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Cocina</t>
         </is>
       </c>
       <c r="D24" s="11" t="n"/>
@@ -1950,12 +2004,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Calendario de colaboraciones con bodegas</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Sumiller</t>
+          <t>Servicio exclusivo: personal asignado</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Servicio</t>
         </is>
       </c>
       <c r="D25" s="11" t="n"/>
@@ -1969,12 +2023,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Calendario de pop-ups y showcookings</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>Eventos</t>
+          <t>Decoración especial de la mesa/sala</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Sala</t>
         </is>
       </c>
       <c r="D26" s="11" t="n"/>
@@ -1983,57 +2037,198 @@
       <c r="G26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="20" t="inlineStr">
+      <c r="A27" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Cerrar la facturación al terminar la cena: extras realmente consumidos, señal ya cobrada descontada e IVA aplicado</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>📅 CALENDARIO ANUAL DE EVENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Planificar eventos por trimestre (mín. 1/mes)</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Presupuesto anual de eventos especiales</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Calendario de colaboraciones con bodegas</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Sumiller</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Calendario de pop-ups y showcookings</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Eventos</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C27">
-        <f>COUNTIF(E6:E26,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C35">
+        <f>COUNTIFS(B6:B34,"?*",E6:E34,"✓")-COUNTIFS(B6:B34,"Tarea",E6:E34,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E27">
-        <f>COUNTIF(B6:B26,"?*")</f>
-        <v>17.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="E35">
+        <f>COUNTIF(B6:B34,"?*")-COUNTIF(B6:B34,"Tarea")-COUNTIF(E6:E34,"N/A")</f>
+        <v>21.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G26">
+  <conditionalFormatting sqref="A6:G34">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E23 E24 E25 E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E23 E24 E25 E26 E27 E31 E32 E33 E34" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-restaurante-creativo/07-chefs-table-eventos.xlsx
+++ b/astro-site/public/dl/kit-tareas-restaurante-creativo/07-chefs-table-eventos.xlsx
@@ -2215,10 +2215,10 @@
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A37:G37"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
   <conditionalFormatting sqref="A6:G34">
